--- a/pandemic-loss-modeling/exceedance_results/marani_inspired.xlsx
+++ b/pandemic-loss-modeling/exceedance_results/marani_inspired.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -390,7 +390,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>0.001</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
         <v>0.1</v>
@@ -398,81 +398,73 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>0.002</v>
+        <v>7.2</v>
       </c>
       <c r="B3">
-        <v>0.1</v>
+        <v>0.03193750680089951</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>7.2</v>
+        <v>28</v>
       </c>
       <c r="B4">
-        <v>0.03193750680089951</v>
+        <v>0.01415983943143759</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="B5">
-        <v>0.01415983943143759</v>
+        <v>0.01044594645720733</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="B6">
-        <v>0.01044594645720733</v>
+        <v>0.006842707606711684</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="B7">
-        <v>0.006842707606711684</v>
+        <v>0.004738001287579652</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="B8">
-        <v>0.004738001287579652</v>
+        <v>0.003914131943086718</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="B9">
-        <v>0.003914131943086718</v>
+        <v>0.00367372088563116</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="B10">
-        <v>0.00367372088563116</v>
+        <v>0.003374066102675855</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="B11">
-        <v>0.003374066102675855</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12">
-        <v>280</v>
-      </c>
-      <c r="B12">
         <v>0.00312873460665627</v>
       </c>
     </row>

--- a/pandemic-loss-modeling/exceedance_results/marani_inspired.xlsx
+++ b/pandemic-loss-modeling/exceedance_results/marani_inspired.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -398,73 +398,217 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>7.2</v>
+        <v>0.04</v>
       </c>
       <c r="B3">
-        <v>0.03193750680089951</v>
+        <v>0.09876340068890241</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>28</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="B4">
-        <v>0.01415983943143759</v>
+        <v>0.09756422235529666</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>45</v>
+        <v>0.08</v>
       </c>
       <c r="B5">
-        <v>0.01044594645720733</v>
+        <v>0.09717250128819317</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>86</v>
+        <v>0.1</v>
       </c>
       <c r="B6">
-        <v>0.006842707606711684</v>
+        <v>0.09640068676341217</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>150</v>
+        <v>0.4</v>
       </c>
       <c r="B7">
-        <v>0.004738001287579652</v>
+        <v>0.08640563017254604</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>200</v>
+        <v>0.7</v>
       </c>
       <c r="B8">
-        <v>0.003914131943086718</v>
+        <v>0.07864836626494794</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>220</v>
+        <v>1</v>
       </c>
       <c r="B9">
-        <v>0.00367372088563116</v>
+        <v>0.07242230547044784</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>250</v>
+        <v>4</v>
       </c>
       <c r="B10">
-        <v>0.003374066102675855</v>
+        <v>0.04325321978630998</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>0.03243387357577674</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0.02653557910330467</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>28</v>
+      </c>
+      <c r="B13">
+        <v>0.01415983943143759</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>40</v>
+      </c>
+      <c r="B14">
+        <v>0.01127163259925531</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>45</v>
+      </c>
+      <c r="B15">
+        <v>0.01044594645720733</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>70</v>
+      </c>
+      <c r="B16">
+        <v>0.007833062606051855</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>86</v>
+      </c>
+      <c r="B17">
+        <v>0.006842707606711684</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>100</v>
+      </c>
+      <c r="B18">
+        <v>0.006195478274538336</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>120</v>
+      </c>
+      <c r="B19">
+        <v>0.005492552641560011</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>150</v>
+      </c>
+      <c r="B20">
+        <v>0.004738001287579652</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>170</v>
+      </c>
+      <c r="B21">
+        <v>0.004360420926985143</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>190</v>
+      </c>
+      <c r="B22">
+        <v>0.004049883421481071</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>200</v>
+      </c>
+      <c r="B23">
+        <v>0.003914131943086718</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>220</v>
+      </c>
+      <c r="B24">
+        <v>0.00367372088563116</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>240</v>
+      </c>
+      <c r="B25">
+        <v>0.003467028115053594</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>250</v>
+      </c>
+      <c r="B26">
+        <v>0.003374066102675855</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>260</v>
+      </c>
+      <c r="B27">
+        <v>0.003287077566970043</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>270</v>
+      </c>
+      <c r="B28">
+        <v>0.003205471555867668</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
         <v>280</v>
       </c>
-      <c r="B11">
+      <c r="B29">
         <v>0.00312873460665627</v>
       </c>
     </row>

--- a/pandemic-loss-modeling/exceedance_results/marani_inspired.xlsx
+++ b/pandemic-loss-modeling/exceedance_results/marani_inspired.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -470,145 +470,177 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B12">
-        <v>0.02653557910330467</v>
+        <v>0.03012675782365279</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="B13">
-        <v>0.01415983943143759</v>
+        <v>0.02653557910330467</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="B14">
-        <v>0.01127163259925531</v>
+        <v>0.02086669465001545</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="B15">
-        <v>0.01044594645720733</v>
+        <v>0.01749002149411094</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="B16">
-        <v>0.007833062606051855</v>
+        <v>0.01415983943143759</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="B17">
-        <v>0.006842707606711684</v>
+        <v>0.01127163259925531</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="B18">
-        <v>0.006195478274538336</v>
+        <v>0.01044594645720733</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="B19">
-        <v>0.005492552641560011</v>
+        <v>0.007833062606051855</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>150</v>
+        <v>86</v>
       </c>
       <c r="B20">
-        <v>0.004738001287579652</v>
+        <v>0.006842707606711684</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="B21">
-        <v>0.004360420926985143</v>
+        <v>0.006195478274538336</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="B22">
-        <v>0.004049883421481071</v>
+        <v>0.005492552641560011</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="B23">
-        <v>0.003914131943086718</v>
+        <v>0.004738001287579652</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="B24">
-        <v>0.00367372088563116</v>
+        <v>0.004360420926985143</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>240</v>
+        <v>190</v>
       </c>
       <c r="B25">
-        <v>0.003467028115053594</v>
+        <v>0.004049883421481071</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="B26">
-        <v>0.003374066102675855</v>
+        <v>0.003914131943086718</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="B27">
-        <v>0.003287077566970043</v>
+        <v>0.00367372088563116</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="B28">
-        <v>0.003205471555867668</v>
+        <v>0.003566647565128345</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
+        <v>240</v>
+      </c>
+      <c r="B29">
+        <v>0.003467028115053594</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>250</v>
+      </c>
+      <c r="B30">
+        <v>0.003374066102675855</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>260</v>
+      </c>
+      <c r="B31">
+        <v>0.003287077566970043</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>270</v>
+      </c>
+      <c r="B32">
+        <v>0.003205471555867668</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
         <v>280</v>
       </c>
-      <c r="B29">
+      <c r="B33">
         <v>0.00312873460665627</v>
       </c>
     </row>
